--- a/Iteration_2/Echo_Review/Echo/project_tracker_matchmaking_leaderboard.xlsx
+++ b/Iteration_2/Echo_Review/Echo/project_tracker_matchmaking_leaderboard.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0CB76D6-0BCE-498D-90FA-945819F8D11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C651F6-1251-464C-B1E3-D0C37A153E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project tracker" sheetId="1" r:id="rId1"/>
@@ -38,6 +38,60 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={54407567-1572-4EF0-84D1-2F7A50100333}</author>
+    <author>tc={6D2D7681-AFC1-4F5A-B154-16D74E851623}</author>
+    <author>tc={CD3B299D-F77C-494D-8237-5314B40EACFB}</author>
+    <author>tc={1E40B37D-EE5E-4ABA-94C6-CD6810B21150}</author>
+    <author>tc={7C2A0CDC-391A-406C-A77A-972F9A5E0FF8}</author>
+  </authors>
+  <commentList>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{54407567-1572-4EF0-84D1-2F7A50100333}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The tracker is missing the category section that describes the kind of work being done during each task (Planning, documentation, coding, etc)</t>
+      </text>
+    </comment>
+    <comment ref="G7" authorId="1" shapeId="0" xr:uid="{6D2D7681-AFC1-4F5A-B154-16D74E851623}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Student 2’s estimated work duration in days is formatted a bit weird. The minimum duration in days should be 1, so I assume that’s what the student meant, but it would be better to list it as 1 instead of 0 for consistency and organization</t>
+      </text>
+    </comment>
+    <comment ref="D9" authorId="2" shapeId="0" xr:uid="{CD3B299D-F77C-494D-8237-5314B40EACFB}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Student 3’s estimated start and finish date for their tasks doesn’t match the estimated duration in days. Furthermore, they started late, on the day of the deadline. While the workload was less than expected and the deadline was met, this may be a sign of procrastination that should be addressed</t>
+      </text>
+    </comment>
+    <comment ref="L9" authorId="3" shapeId="0" xr:uid="{1E40B37D-EE5E-4ABA-94C6-CD6810B21150}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Student 3’s tasks have no notes. It would be helpful to have them to describe the tasks that student 3 has done and better track the overall state and progress of the project</t>
+      </text>
+    </comment>
+    <comment ref="B11" authorId="4" shapeId="0" xr:uid="{7C2A0CDC-391A-406C-A77A-972F9A5E0FF8}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    It seems Student 3 started work on the code before making the use case descriptions and structure diagram. It would be better to do these in reverse order to better structure the code before making it.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="47">
   <si>
@@ -191,7 +245,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;Over/Under flag&quot;;&quot;&quot;;&quot;&quot;"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="3" tint="-0.499984740745262"/>
@@ -632,6 +686,19 @@
   </cellStyles>
   <dxfs count="26">
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -723,7 +790,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
       <alignment horizontal="left" vertical="center" textRotation="0" indent="2" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -743,7 +810,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
       <alignment horizontal="left" vertical="center" textRotation="0" indent="2" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -807,7 +874,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
       <alignment horizontal="left" vertical="center" textRotation="0" indent="2" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -827,7 +894,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
       <alignment horizontal="left" vertical="center" textRotation="0" indent="2" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -905,19 +972,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="2" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color auto="1"/>
-      </font>
     </dxf>
     <dxf>
       <fill>
@@ -1211,7 +1265,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProjectTracker" displayName="ProjectTracker" ref="B4:L11" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProjectTracker" displayName="ProjectTracker" ref="B4:L11" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <autoFilter ref="B4:L11" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -1226,21 +1280,21 @@
     <filterColumn colId="10" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Task" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Assigned to" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Estimated start" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Estimated finish" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Estimated work (in hours)" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Estimated duration_x000a_(in days)" dataDxfId="9">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Task" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Assigned to" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Estimated start" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Estimated finish" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Estimated work (in hours)" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Estimated duration_x000a_(in days)" dataDxfId="11">
       <calculatedColumnFormula>IF(COUNTA('Project tracker'!$D5,'Project tracker'!$E5)&lt;&gt;2,"",DAYS360('Project tracker'!$D5,'Project tracker'!$E5,FALSE))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Actual start" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Actual finish" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actual work _x000a_(in hours)" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Actual duration (in days)" dataDxfId="5">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Actual start" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Actual finish" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actual work _x000a_(in hours)" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Actual duration (in days)" dataDxfId="7">
       <calculatedColumnFormula>IF(COUNTA('Project tracker'!$H5,'Project tracker'!$I5)&lt;&gt;2,"",DAYS360('Project tracker'!$H5,'Project tracker'!$I5,FALSE))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Notes" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Notes" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="Custom Table Style" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -1252,14 +1306,14 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="CategoryAndEmployeeTable" displayName="CategoryAndEmployeeTable" ref="B4:C10" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="CategoryAndEmployeeTable" displayName="CategoryAndEmployeeTable" ref="B4:C10" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="B4:C10" xr:uid="{00000000-0009-0000-0100-000003000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Category Name" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Employee Name" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Category Name" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Employee Name" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="Custom Table Style 2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -1495,29 +1549,49 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B5" dT="2024-11-13T03:55:50.42" personId="{00000000-0000-0000-0000-000000000000}" id="{54407567-1572-4EF0-84D1-2F7A50100333}">
+    <text>The tracker is missing the category section that describes the kind of work being done during each task (Planning, documentation, coding, etc)</text>
+  </threadedComment>
+  <threadedComment ref="G7" dT="2024-11-13T02:24:42.52" personId="{00000000-0000-0000-0000-000000000000}" id="{6D2D7681-AFC1-4F5A-B154-16D74E851623}">
+    <text>Student 2’s estimated work duration in days is formatted a bit weird. The minimum duration in days should be 1, so I assume that’s what the student meant, but it would be better to list it as 1 instead of 0 for consistency and organization</text>
+  </threadedComment>
+  <threadedComment ref="D9" dT="2024-11-13T04:11:58.36" personId="{00000000-0000-0000-0000-000000000000}" id="{CD3B299D-F77C-494D-8237-5314B40EACFB}">
+    <text>Student 3’s estimated start and finish date for their tasks doesn’t match the estimated duration in days. Furthermore, they started late, on the day of the deadline. While the workload was less than expected and the deadline was met, this may be a sign of procrastination that should be addressed</text>
+  </threadedComment>
+  <threadedComment ref="L9" dT="2024-11-13T02:22:05.30" personId="{00000000-0000-0000-0000-000000000000}" id="{1E40B37D-EE5E-4ABA-94C6-CD6810B21150}">
+    <text>Student 3’s tasks have no notes. It would be helpful to have them to describe the tasks that student 3 has done and better track the overall state and progress of the project</text>
+  </threadedComment>
+  <threadedComment ref="B11" dT="2024-11-13T03:14:23.49" personId="{00000000-0000-0000-0000-000000000000}" id="{7C2A0CDC-391A-406C-A77A-972F9A5E0FF8}">
+    <text>It seems Student 3 started work on the code before making the use case descriptions and structure diagram. It would be better to do these in reverse order to better structure the code before making it.</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1">
     <tabColor theme="6"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N12"/>
-  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="30" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.69921875" style="3" customWidth="1"/>
-    <col min="2" max="4" width="18.69921875" style="19" customWidth="1"/>
-    <col min="5" max="6" width="18.69921875" style="20" customWidth="1"/>
-    <col min="7" max="8" width="18.69921875" style="19" customWidth="1"/>
-    <col min="9" max="10" width="16.796875" style="20" customWidth="1"/>
+    <col min="1" max="1" width="6.7265625" style="3" customWidth="1"/>
+    <col min="2" max="4" width="18.7265625" style="19" customWidth="1"/>
+    <col min="5" max="6" width="18.7265625" style="20" customWidth="1"/>
+    <col min="7" max="8" width="18.7265625" style="19" customWidth="1"/>
+    <col min="9" max="10" width="16.81640625" style="20" customWidth="1"/>
     <col min="11" max="12" width="16" style="19" customWidth="1"/>
-    <col min="13" max="13" width="20.3984375" style="19" customWidth="1"/>
-    <col min="14" max="14" width="6.69921875" style="3" customWidth="1"/>
-    <col min="15" max="15" width="4.19921875" style="2" customWidth="1"/>
-    <col min="16" max="40" width="3.296875" style="2" customWidth="1"/>
-    <col min="41" max="16384" width="9.09765625" style="2"/>
+    <col min="13" max="13" width="20.36328125" style="19" customWidth="1"/>
+    <col min="14" max="14" width="6.7265625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="4.1796875" style="2" customWidth="1"/>
+    <col min="16" max="40" width="3.26953125" style="2" customWidth="1"/>
+    <col min="41" max="16384" width="9.08984375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="5" customFormat="1" ht="30" customHeight="1">
+    <row r="1" spans="1:14" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -1533,7 +1607,7 @@
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
     </row>
-    <row r="2" spans="1:14" s="5" customFormat="1" ht="80.099999999999994" customHeight="1">
+    <row r="2" spans="1:14" s="5" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="26" t="s">
         <v>0</v>
@@ -1555,7 +1629,7 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
     </row>
-    <row r="3" spans="1:14" s="5" customFormat="1" ht="30" customHeight="1">
+    <row r="3" spans="1:14" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1571,7 +1645,7 @@
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
     </row>
-    <row r="4" spans="1:14" s="5" customFormat="1" ht="62.1" customHeight="1">
+    <row r="4" spans="1:14" s="5" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11"/>
       <c r="B4" s="17" t="s">
         <v>2</v>
@@ -1608,7 +1682,7 @@
       </c>
       <c r="M4" s="11"/>
     </row>
-    <row r="5" spans="1:14" s="5" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="5" spans="1:14" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="18" t="s">
         <v>13</v>
@@ -1647,7 +1721,7 @@
       </c>
       <c r="M5" s="3"/>
     </row>
-    <row r="6" spans="1:14" s="5" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="6" spans="1:14" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="18" t="s">
         <v>16</v>
@@ -1686,7 +1760,7 @@
       </c>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" spans="1:14" s="5" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="7" spans="1:14" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="18" t="s">
         <v>18</v>
@@ -1696,11 +1770,11 @@
       </c>
       <c r="D7" s="25">
         <f ca="1">TODAY()-4</f>
-        <v>45597</v>
+        <v>45604</v>
       </c>
       <c r="E7" s="25">
         <f ca="1">TODAY()-4</f>
-        <v>45597</v>
+        <v>45604</v>
       </c>
       <c r="F7" s="18">
         <v>1</v>
@@ -1711,11 +1785,11 @@
       </c>
       <c r="H7" s="25">
         <f ca="1">TODAY()-4</f>
-        <v>45597</v>
+        <v>45604</v>
       </c>
       <c r="I7" s="25">
         <f ca="1">TODAY()-4</f>
-        <v>45597</v>
+        <v>45604</v>
       </c>
       <c r="J7" s="18">
         <v>1</v>
@@ -1728,7 +1802,7 @@
       </c>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" spans="1:14" s="5" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="8" spans="1:14" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="18" t="s">
         <v>21</v>
@@ -1738,11 +1812,11 @@
       </c>
       <c r="D8" s="25">
         <f ca="1">TODAY()-3</f>
-        <v>45598</v>
+        <v>45605</v>
       </c>
       <c r="E8" s="25">
         <f ca="1">TODAY()-3</f>
-        <v>45598</v>
+        <v>45605</v>
       </c>
       <c r="F8" s="18">
         <v>3</v>
@@ -1753,11 +1827,11 @@
       </c>
       <c r="H8" s="25">
         <f ca="1">TODAY()-3</f>
-        <v>45598</v>
+        <v>45605</v>
       </c>
       <c r="I8" s="25">
         <f ca="1">TODAY()-3</f>
-        <v>45598</v>
+        <v>45605</v>
       </c>
       <c r="J8" s="18">
         <v>5</v>
@@ -1770,7 +1844,7 @@
       </c>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" spans="1:14" s="5" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="9" spans="1:14" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="18" t="s">
         <v>23</v>
@@ -1805,7 +1879,7 @@
       <c r="L9" s="18"/>
       <c r="M9" s="3"/>
     </row>
-    <row r="10" spans="1:14" s="5" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="10" spans="1:14" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="18" t="s">
         <v>25</v>
@@ -1840,7 +1914,7 @@
       <c r="L10" s="18"/>
       <c r="M10" s="3"/>
     </row>
-    <row r="11" spans="1:14" s="5" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="11" spans="1:14" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="18" t="s">
         <v>26</v>
@@ -1876,7 +1950,7 @@
       <c r="L11" s="18"/>
       <c r="M11" s="3"/>
     </row>
-    <row r="12" spans="1:14" s="5" customFormat="1" ht="30" customHeight="1">
+    <row r="12" spans="1:14" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -1894,12 +1968,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="J5:J11">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>(ABS((J5-F5))/F5)&gt;FlagPercent</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K11">
-    <cfRule type="expression" dxfId="17" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>(ABS((K5-G5))/G5)&gt;FlagPercent</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1925,8 +1999,9 @@
   <pageSetup fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter differentFirst="1"/>
   <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1934,15 +2009,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C52F64F2-A0CB-432E-B537-8AB164D6506B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="27" customWidth="1"/>
-    <col min="2" max="2" width="20.09765625" style="27" customWidth="1"/>
-    <col min="3" max="3" width="16.69921875" style="27" customWidth="1"/>
-    <col min="4" max="16384" width="8.69921875" style="27"/>
+    <col min="1" max="1" width="12.7265625" style="27" customWidth="1"/>
+    <col min="2" max="2" width="20.08984375" style="27" customWidth="1"/>
+    <col min="3" max="3" width="16.7265625" style="27" customWidth="1"/>
+    <col min="4" max="16384" width="8.7265625" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
         <v>27</v>
       </c>
@@ -1953,17 +2028,17 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="27" t="s">
         <v>32</v>
       </c>
@@ -1981,21 +2056,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.69921875" style="12" customWidth="1"/>
-    <col min="2" max="3" width="18.5" style="23" customWidth="1"/>
-    <col min="4" max="4" width="6.69921875" style="13" customWidth="1"/>
+    <col min="1" max="1" width="6.7265625" style="12" customWidth="1"/>
+    <col min="2" max="3" width="18.453125" style="23" customWidth="1"/>
+    <col min="4" max="4" width="6.7265625" style="13" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" customFormat="1" ht="30" customHeight="1">
+    <row r="1" spans="1:4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12"/>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
     </row>
-    <row r="2" spans="1:4" customFormat="1" ht="80.099999999999994" customHeight="1">
+    <row r="2" spans="1:4" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="16" t="s">
         <v>33</v>
@@ -2003,13 +2078,13 @@
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
     </row>
-    <row r="3" spans="1:4" customFormat="1" ht="30" customHeight="1">
+    <row r="3" spans="1:4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
     </row>
-    <row r="4" spans="1:4" customFormat="1" ht="62.1" customHeight="1">
+    <row r="4" spans="1:4" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14"/>
       <c r="B4" s="22" t="s">
         <v>34</v>
@@ -2019,7 +2094,7 @@
       </c>
       <c r="D4" s="15"/>
     </row>
-    <row r="5" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="5" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12"/>
       <c r="B5" s="22" t="s">
         <v>36</v>
@@ -2029,7 +2104,7 @@
       </c>
       <c r="D5" s="13"/>
     </row>
-    <row r="6" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="6" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12"/>
       <c r="B6" s="22" t="s">
         <v>38</v>
@@ -2039,7 +2114,7 @@
       </c>
       <c r="D6" s="13"/>
     </row>
-    <row r="7" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="7" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12"/>
       <c r="B7" s="22" t="s">
         <v>40</v>
@@ -2049,7 +2124,7 @@
       </c>
       <c r="D7" s="13"/>
     </row>
-    <row r="8" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="8" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12"/>
       <c r="B8" s="22" t="s">
         <v>41</v>
@@ -2059,7 +2134,7 @@
       </c>
       <c r="D8" s="13"/>
     </row>
-    <row r="9" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="9" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12"/>
       <c r="B9" s="22" t="s">
         <v>43</v>
@@ -2069,7 +2144,7 @@
       </c>
       <c r="D9" s="13"/>
     </row>
-    <row r="10" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="10" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="22" t="s">
         <v>45</v>
@@ -2079,7 +2154,7 @@
       </c>
       <c r="D10" s="13"/>
     </row>
-    <row r="11" spans="1:4" customFormat="1" ht="30" customHeight="1">
+    <row r="11" spans="1:4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
@@ -2101,6 +2176,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -2120,7 +2204,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -2432,25 +2516,45 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9066C173-72E5-4455-ACFB-9A7596D30A2B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{648F31BC-5AA3-42BF-80F4-A797E59C4FBD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D99023F8-0F96-4650-8DC3-63EE0BD6CB59}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9066C173-72E5-4455-ACFB-9A7596D30A2B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{648F31BC-5AA3-42BF-80F4-A797E59C4FBD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D99023F8-0F96-4650-8DC3-63EE0BD6CB59}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Iteration_2/Echo_Review/Echo/project_tracker_matchmaking_leaderboard.xlsx
+++ b/Iteration_2/Echo_Review/Echo/project_tracker_matchmaking_leaderboard.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C651F6-1251-464C-B1E3-D0C37A153E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EEF3764-4837-46C9-A742-0C129459353D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,8 +44,9 @@
     <author>tc={54407567-1572-4EF0-84D1-2F7A50100333}</author>
     <author>tc={6D2D7681-AFC1-4F5A-B154-16D74E851623}</author>
     <author>tc={CD3B299D-F77C-494D-8237-5314B40EACFB}</author>
+    <author>tc={9717BCA1-AFAA-4CBA-9F0B-F41FAF647A1C}</author>
     <author>tc={1E40B37D-EE5E-4ABA-94C6-CD6810B21150}</author>
-    <author>tc={7C2A0CDC-391A-406C-A77A-972F9A5E0FF8}</author>
+    <author>tc={148159F2-9102-4E85-BF1B-E8AE6420CBA1}</author>
   </authors>
   <commentList>
     <comment ref="B5" authorId="0" shapeId="0" xr:uid="{54407567-1572-4EF0-84D1-2F7A50100333}">
@@ -69,10 +70,18 @@
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Student 3’s estimated start and finish date for their tasks doesn’t match the estimated duration in days. Furthermore, they started late, on the day of the deadline. While the workload was less than expected and the deadline was met, this may be a sign of procrastination that should be addressed</t>
+    Student 3’s estimated start and finish date for their tasks doesn’t match the estimated duration in days. This should be changed so that the expected start and finish dates should better align with the estimated duration</t>
       </text>
     </comment>
-    <comment ref="L9" authorId="3" shapeId="0" xr:uid="{1E40B37D-EE5E-4ABA-94C6-CD6810B21150}">
+    <comment ref="H9" authorId="3" shapeId="0" xr:uid="{9717BCA1-AFAA-4CBA-9F0B-F41FAF647A1C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    According to the actual start dates, Student 3 started late, beginning on the day of the deadline. While the workload was less than expected and the deadline was met, this could be a sign of procrastination or rushed inadequate work and  should be addressed to see if the late start was the cause of student 3’s work ethic, a mistake in forgetting to adjust the expected start dates (as they don’t match the expected duration in days), or external matters.</t>
+      </text>
+    </comment>
+    <comment ref="L9" authorId="4" shapeId="0" xr:uid="{1E40B37D-EE5E-4ABA-94C6-CD6810B21150}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -80,12 +89,13 @@
     Student 3’s tasks have no notes. It would be helpful to have them to describe the tasks that student 3 has done and better track the overall state and progress of the project</t>
       </text>
     </comment>
-    <comment ref="B11" authorId="4" shapeId="0" xr:uid="{7C2A0CDC-391A-406C-A77A-972F9A5E0FF8}">
+    <comment ref="H11" authorId="5" shapeId="0" xr:uid="{148159F2-9102-4E85-BF1B-E8AE6420CBA1}">
       <text>
-        <t>[Threaded comment]
+        <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    It seems Student 3 started work on the code before making the use case descriptions and structure diagram. It would be better to do these in reverse order to better structure the code before making it.</t>
+    It seems Student 3 started work on the code before making the use case descriptions and structure diagram. It would be better to do these in reverse order to better structure the code before making it.
+</t>
       </text>
     </comment>
   </commentList>
@@ -245,7 +255,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;Over/Under flag&quot;;&quot;&quot;;&quot;&quot;"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="3" tint="-0.499984740745262"/>
@@ -399,6 +409,12 @@
       <color theme="9" tint="-0.499984740745262"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1264,6 +1280,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProjectTracker" displayName="ProjectTracker" ref="B4:L11" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <autoFilter ref="B4:L11" xr:uid="{00000000-0009-0000-0100-000001000000}">
@@ -1558,13 +1578,17 @@
     <text>Student 2’s estimated work duration in days is formatted a bit weird. The minimum duration in days should be 1, so I assume that’s what the student meant, but it would be better to list it as 1 instead of 0 for consistency and organization</text>
   </threadedComment>
   <threadedComment ref="D9" dT="2024-11-13T04:11:58.36" personId="{00000000-0000-0000-0000-000000000000}" id="{CD3B299D-F77C-494D-8237-5314B40EACFB}">
-    <text>Student 3’s estimated start and finish date for their tasks doesn’t match the estimated duration in days. Furthermore, they started late, on the day of the deadline. While the workload was less than expected and the deadline was met, this may be a sign of procrastination that should be addressed</text>
+    <text>Student 3’s estimated start and finish date for their tasks doesn’t match the estimated duration in days. This should be changed so that the expected start and finish dates should better align with the estimated duration</text>
+  </threadedComment>
+  <threadedComment ref="H9" dT="2024-11-14T04:12:11.23" personId="{00000000-0000-0000-0000-000000000000}" id="{9717BCA1-AFAA-4CBA-9F0B-F41FAF647A1C}">
+    <text>According to the actual start dates, Student 3 started late, beginning on the day of the deadline. While the workload was less than expected and the deadline was met, this could be a sign of procrastination or rushed inadequate work and  should be addressed to see if the late start was the cause of student 3’s work ethic, a mistake in forgetting to adjust the expected start dates (as they don’t match the expected duration in days), or external matters.</text>
   </threadedComment>
   <threadedComment ref="L9" dT="2024-11-13T02:22:05.30" personId="{00000000-0000-0000-0000-000000000000}" id="{1E40B37D-EE5E-4ABA-94C6-CD6810B21150}">
     <text>Student 3’s tasks have no notes. It would be helpful to have them to describe the tasks that student 3 has done and better track the overall state and progress of the project</text>
   </threadedComment>
-  <threadedComment ref="B11" dT="2024-11-13T03:14:23.49" personId="{00000000-0000-0000-0000-000000000000}" id="{7C2A0CDC-391A-406C-A77A-972F9A5E0FF8}">
-    <text>It seems Student 3 started work on the code before making the use case descriptions and structure diagram. It would be better to do these in reverse order to better structure the code before making it.</text>
+  <threadedComment ref="H11" dT="2024-11-14T04:03:16.07" personId="{00000000-0000-0000-0000-000000000000}" id="{148159F2-9102-4E85-BF1B-E8AE6420CBA1}">
+    <text xml:space="preserve">It seems Student 3 started work on the code before making the use case descriptions and structure diagram. It would be better to do these in reverse order to better structure the code before making it.
+</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -1770,11 +1794,11 @@
       </c>
       <c r="D7" s="25">
         <f ca="1">TODAY()-4</f>
-        <v>45604</v>
+        <v>45605</v>
       </c>
       <c r="E7" s="25">
         <f ca="1">TODAY()-4</f>
-        <v>45604</v>
+        <v>45605</v>
       </c>
       <c r="F7" s="18">
         <v>1</v>
@@ -1785,11 +1809,11 @@
       </c>
       <c r="H7" s="25">
         <f ca="1">TODAY()-4</f>
-        <v>45604</v>
+        <v>45605</v>
       </c>
       <c r="I7" s="25">
         <f ca="1">TODAY()-4</f>
-        <v>45604</v>
+        <v>45605</v>
       </c>
       <c r="J7" s="18">
         <v>1</v>
@@ -1812,11 +1836,11 @@
       </c>
       <c r="D8" s="25">
         <f ca="1">TODAY()-3</f>
-        <v>45605</v>
+        <v>45606</v>
       </c>
       <c r="E8" s="25">
         <f ca="1">TODAY()-3</f>
-        <v>45605</v>
+        <v>45606</v>
       </c>
       <c r="F8" s="18">
         <v>3</v>
@@ -1827,11 +1851,11 @@
       </c>
       <c r="H8" s="25">
         <f ca="1">TODAY()-3</f>
-        <v>45605</v>
+        <v>45606</v>
       </c>
       <c r="I8" s="25">
         <f ca="1">TODAY()-3</f>
-        <v>45605</v>
+        <v>45606</v>
       </c>
       <c r="J8" s="18">
         <v>5</v>
@@ -2176,15 +2200,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -2202,6 +2217,15 @@
     <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2517,14 +2541,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{648F31BC-5AA3-42BF-80F4-A797E59C4FBD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9066C173-72E5-4455-ACFB-9A7596D30A2B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -2532,6 +2548,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
     <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
     <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{648F31BC-5AA3-42BF-80F4-A797E59C4FBD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Iteration_2/Echo_Review/Echo/project_tracker_matchmaking_leaderboard.xlsx
+++ b/Iteration_2/Echo_Review/Echo/project_tracker_matchmaking_leaderboard.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EEF3764-4837-46C9-A742-0C129459353D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345C0D5B-3956-4E92-A84C-14C4ED877C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,8 @@
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Student 2’s estimated work duration in days is formatted a bit weird. The minimum duration in days should be 1, so I assume that’s what the student meant, but it would be better to list it as 1 instead of 0 for consistency and organization</t>
+    Student 2’s estimated work duration in days is formatted a bit weird. The minimum duration in days should be 1, so I assume that’s what the student meant, but it would be better to list it as 1 instead of 0 for consistency and organization.
+Not a big deal though</t>
       </text>
     </comment>
     <comment ref="D9" authorId="2" shapeId="0" xr:uid="{CD3B299D-F77C-494D-8237-5314B40EACFB}">
@@ -102,6 +103,42 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={0430417D-6521-4777-A475-87A4377C5536}</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{0430417D-6521-4777-A475-87A4377C5536}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Task lookup page incomplete</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={DC7AA41F-FB8B-4CD3-BD51-6F9F13C9B524}</author>
+  </authors>
+  <commentList>
+    <comment ref="C7" authorId="0" shapeId="0" xr:uid="{DC7AA41F-FB8B-4CD3-BD51-6F9F13C9B524}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Only two students are named and the categories aren’t listed</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="47">
   <si>
@@ -255,7 +292,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;Over/Under flag&quot;;&quot;&quot;;&quot;&quot;"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="3" tint="-0.499984740745262"/>
@@ -409,12 +446,6 @@
       <color theme="9" tint="-0.499984740745262"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1575,7 +1606,8 @@
     <text>The tracker is missing the category section that describes the kind of work being done during each task (Planning, documentation, coding, etc)</text>
   </threadedComment>
   <threadedComment ref="G7" dT="2024-11-13T02:24:42.52" personId="{00000000-0000-0000-0000-000000000000}" id="{6D2D7681-AFC1-4F5A-B154-16D74E851623}">
-    <text>Student 2’s estimated work duration in days is formatted a bit weird. The minimum duration in days should be 1, so I assume that’s what the student meant, but it would be better to list it as 1 instead of 0 for consistency and organization</text>
+    <text>Student 2’s estimated work duration in days is formatted a bit weird. The minimum duration in days should be 1, so I assume that’s what the student meant, but it would be better to list it as 1 instead of 0 for consistency and organization.
+Not a big deal though</text>
   </threadedComment>
   <threadedComment ref="D9" dT="2024-11-13T04:11:58.36" personId="{00000000-0000-0000-0000-000000000000}" id="{CD3B299D-F77C-494D-8237-5314B40EACFB}">
     <text>Student 3’s estimated start and finish date for their tasks doesn’t match the estimated duration in days. This should be changed so that the expected start and finish dates should better align with the estimated duration</text>
@@ -1589,6 +1621,22 @@
   <threadedComment ref="H11" dT="2024-11-14T04:03:16.07" personId="{00000000-0000-0000-0000-000000000000}" id="{148159F2-9102-4E85-BF1B-E8AE6420CBA1}">
     <text xml:space="preserve">It seems Student 3 started work on the code before making the use case descriptions and structure diagram. It would be better to do these in reverse order to better structure the code before making it.
 </text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A1" dT="2024-11-14T04:21:50.19" personId="{00000000-0000-0000-0000-000000000000}" id="{0430417D-6521-4777-A475-87A4377C5536}">
+    <text>Task lookup page incomplete</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C7" dT="2024-11-14T04:20:11.21" personId="{00000000-0000-0000-0000-000000000000}" id="{DC7AA41F-FB8B-4CD3-BD51-6F9F13C9B524}">
+    <text>Only two students are named and the categories aren’t listed</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -2031,7 +2079,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C52F64F2-A0CB-432E-B537-8AB164D6506B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C52F64F2-A0CB-432E-B537-8AB164D6506B}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2070,11 +2118,12 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2">
     <tabColor theme="7" tint="0.59999389629810485"/>
     <pageSetUpPr fitToPage="1"/>
@@ -2193,13 +2242,23 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -2217,15 +2276,6 @@
     <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2541,6 +2591,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{648F31BC-5AA3-42BF-80F4-A797E59C4FBD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9066C173-72E5-4455-ACFB-9A7596D30A2B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -2548,14 +2606,6 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
     <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
     <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{648F31BC-5AA3-42BF-80F4-A797E59C4FBD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Iteration_2/Echo_Review/Echo/project_tracker_matchmaking_leaderboard.xlsx
+++ b/Iteration_2/Echo_Review/Echo/project_tracker_matchmaking_leaderboard.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345C0D5B-3956-4E92-A84C-14C4ED877C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1852A5D3-2D31-41FB-B570-3C70AFB54719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -79,7 +79,7 @@
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    According to the actual start dates, Student 3 started late, beginning on the day of the deadline. While the workload was less than expected and the deadline was met, this could be a sign of procrastination or rushed inadequate work and  should be addressed to see if the late start was the cause of student 3’s work ethic, a mistake in forgetting to adjust the expected start dates (as they don’t match the expected duration in days), or external matters.</t>
+    According to the actual start dates, Student 3 started late, beginning on the day of the deadline. While the workload was less than expected and the deadline was met, this discrepancy should be addressed. If it was caused by forgetting to change the estimated start date (as the estimated start and end don’t match the estimated duration), then adjust the estimated start date to match actual start and estimated duration</t>
       </text>
     </comment>
     <comment ref="L9" authorId="4" shapeId="0" xr:uid="{1E40B37D-EE5E-4ABA-94C6-CD6810B21150}">
@@ -1613,7 +1613,7 @@
     <text>Student 3’s estimated start and finish date for their tasks doesn’t match the estimated duration in days. This should be changed so that the expected start and finish dates should better align with the estimated duration</text>
   </threadedComment>
   <threadedComment ref="H9" dT="2024-11-14T04:12:11.23" personId="{00000000-0000-0000-0000-000000000000}" id="{9717BCA1-AFAA-4CBA-9F0B-F41FAF647A1C}">
-    <text>According to the actual start dates, Student 3 started late, beginning on the day of the deadline. While the workload was less than expected and the deadline was met, this could be a sign of procrastination or rushed inadequate work and  should be addressed to see if the late start was the cause of student 3’s work ethic, a mistake in forgetting to adjust the expected start dates (as they don’t match the expected duration in days), or external matters.</text>
+    <text>According to the actual start dates, Student 3 started late, beginning on the day of the deadline. While the workload was less than expected and the deadline was met, this discrepancy should be addressed. If it was caused by forgetting to change the estimated start date (as the estimated start and end don’t match the estimated duration), then adjust the estimated start date to match actual start and estimated duration</text>
   </threadedComment>
   <threadedComment ref="L9" dT="2024-11-13T02:22:05.30" personId="{00000000-0000-0000-0000-000000000000}" id="{1E40B37D-EE5E-4ABA-94C6-CD6810B21150}">
     <text>Student 3’s tasks have no notes. It would be helpful to have them to describe the tasks that student 3 has done and better track the overall state and progress of the project</text>

--- a/Iteration_2/Echo_Review/Echo/project_tracker_matchmaking_leaderboard.xlsx
+++ b/Iteration_2/Echo_Review/Echo/project_tracker_matchmaking_leaderboard.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0CB76D6-0BCE-498D-90FA-945819F8D11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1852A5D3-2D31-41FB-B570-3C70AFB54719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project tracker" sheetId="1" r:id="rId1"/>
@@ -38,6 +38,107 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={54407567-1572-4EF0-84D1-2F7A50100333}</author>
+    <author>tc={6D2D7681-AFC1-4F5A-B154-16D74E851623}</author>
+    <author>tc={CD3B299D-F77C-494D-8237-5314B40EACFB}</author>
+    <author>tc={9717BCA1-AFAA-4CBA-9F0B-F41FAF647A1C}</author>
+    <author>tc={1E40B37D-EE5E-4ABA-94C6-CD6810B21150}</author>
+    <author>tc={148159F2-9102-4E85-BF1B-E8AE6420CBA1}</author>
+  </authors>
+  <commentList>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{54407567-1572-4EF0-84D1-2F7A50100333}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The tracker is missing the category section that describes the kind of work being done during each task (Planning, documentation, coding, etc)</t>
+      </text>
+    </comment>
+    <comment ref="G7" authorId="1" shapeId="0" xr:uid="{6D2D7681-AFC1-4F5A-B154-16D74E851623}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Student 2’s estimated work duration in days is formatted a bit weird. The minimum duration in days should be 1, so I assume that’s what the student meant, but it would be better to list it as 1 instead of 0 for consistency and organization.
+Not a big deal though</t>
+      </text>
+    </comment>
+    <comment ref="D9" authorId="2" shapeId="0" xr:uid="{CD3B299D-F77C-494D-8237-5314B40EACFB}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Student 3’s estimated start and finish date for their tasks doesn’t match the estimated duration in days. This should be changed so that the expected start and finish dates should better align with the estimated duration</t>
+      </text>
+    </comment>
+    <comment ref="H9" authorId="3" shapeId="0" xr:uid="{9717BCA1-AFAA-4CBA-9F0B-F41FAF647A1C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    According to the actual start dates, Student 3 started late, beginning on the day of the deadline. While the workload was less than expected and the deadline was met, this discrepancy should be addressed. If it was caused by forgetting to change the estimated start date (as the estimated start and end don’t match the estimated duration), then adjust the estimated start date to match actual start and estimated duration</t>
+      </text>
+    </comment>
+    <comment ref="L9" authorId="4" shapeId="0" xr:uid="{1E40B37D-EE5E-4ABA-94C6-CD6810B21150}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Student 3’s tasks have no notes. It would be helpful to have them to describe the tasks that student 3 has done and better track the overall state and progress of the project</t>
+      </text>
+    </comment>
+    <comment ref="H11" authorId="5" shapeId="0" xr:uid="{148159F2-9102-4E85-BF1B-E8AE6420CBA1}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    It seems Student 3 started work on the code before making the use case descriptions and structure diagram. It would be better to do these in reverse order to better structure the code before making it.
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={0430417D-6521-4777-A475-87A4377C5536}</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{0430417D-6521-4777-A475-87A4377C5536}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Task lookup page incomplete</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={DC7AA41F-FB8B-4CD3-BD51-6F9F13C9B524}</author>
+  </authors>
+  <commentList>
+    <comment ref="C7" authorId="0" shapeId="0" xr:uid="{DC7AA41F-FB8B-4CD3-BD51-6F9F13C9B524}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Only two students are named and the categories aren’t listed</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="47">
   <si>
@@ -191,7 +292,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;Over/Under flag&quot;;&quot;&quot;;&quot;&quot;"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="3" tint="-0.499984740745262"/>
@@ -632,6 +733,19 @@
   </cellStyles>
   <dxfs count="26">
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -723,7 +837,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
       <alignment horizontal="left" vertical="center" textRotation="0" indent="2" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -743,7 +857,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
       <alignment horizontal="left" vertical="center" textRotation="0" indent="2" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -807,7 +921,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
       <alignment horizontal="left" vertical="center" textRotation="0" indent="2" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -827,7 +941,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
       <alignment horizontal="left" vertical="center" textRotation="0" indent="2" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -905,19 +1019,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="2" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color auto="1"/>
-      </font>
     </dxf>
     <dxf>
       <fill>
@@ -1210,8 +1311,12 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProjectTracker" displayName="ProjectTracker" ref="B4:L11" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProjectTracker" displayName="ProjectTracker" ref="B4:L11" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <autoFilter ref="B4:L11" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -1226,21 +1331,21 @@
     <filterColumn colId="10" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Task" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Assigned to" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Estimated start" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Estimated finish" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Estimated work (in hours)" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Estimated duration_x000a_(in days)" dataDxfId="9">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Task" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Assigned to" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Estimated start" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Estimated finish" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Estimated work (in hours)" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Estimated duration_x000a_(in days)" dataDxfId="11">
       <calculatedColumnFormula>IF(COUNTA('Project tracker'!$D5,'Project tracker'!$E5)&lt;&gt;2,"",DAYS360('Project tracker'!$D5,'Project tracker'!$E5,FALSE))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Actual start" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Actual finish" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actual work _x000a_(in hours)" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Actual duration (in days)" dataDxfId="5">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Actual start" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Actual finish" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Actual work _x000a_(in hours)" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Actual duration (in days)" dataDxfId="7">
       <calculatedColumnFormula>IF(COUNTA('Project tracker'!$H5,'Project tracker'!$I5)&lt;&gt;2,"",DAYS360('Project tracker'!$H5,'Project tracker'!$I5,FALSE))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Notes" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Notes" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="Custom Table Style" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -1252,14 +1357,14 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="CategoryAndEmployeeTable" displayName="CategoryAndEmployeeTable" ref="B4:C10" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="CategoryAndEmployeeTable" displayName="CategoryAndEmployeeTable" ref="B4:C10" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="B4:C10" xr:uid="{00000000-0009-0000-0100-000003000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Category Name" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Employee Name" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Category Name" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Employee Name" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="Custom Table Style 2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -1495,29 +1600,70 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B5" dT="2024-11-13T03:55:50.42" personId="{00000000-0000-0000-0000-000000000000}" id="{54407567-1572-4EF0-84D1-2F7A50100333}">
+    <text>The tracker is missing the category section that describes the kind of work being done during each task (Planning, documentation, coding, etc)</text>
+  </threadedComment>
+  <threadedComment ref="G7" dT="2024-11-13T02:24:42.52" personId="{00000000-0000-0000-0000-000000000000}" id="{6D2D7681-AFC1-4F5A-B154-16D74E851623}">
+    <text>Student 2’s estimated work duration in days is formatted a bit weird. The minimum duration in days should be 1, so I assume that’s what the student meant, but it would be better to list it as 1 instead of 0 for consistency and organization.
+Not a big deal though</text>
+  </threadedComment>
+  <threadedComment ref="D9" dT="2024-11-13T04:11:58.36" personId="{00000000-0000-0000-0000-000000000000}" id="{CD3B299D-F77C-494D-8237-5314B40EACFB}">
+    <text>Student 3’s estimated start and finish date for their tasks doesn’t match the estimated duration in days. This should be changed so that the expected start and finish dates should better align with the estimated duration</text>
+  </threadedComment>
+  <threadedComment ref="H9" dT="2024-11-14T04:12:11.23" personId="{00000000-0000-0000-0000-000000000000}" id="{9717BCA1-AFAA-4CBA-9F0B-F41FAF647A1C}">
+    <text>According to the actual start dates, Student 3 started late, beginning on the day of the deadline. While the workload was less than expected and the deadline was met, this discrepancy should be addressed. If it was caused by forgetting to change the estimated start date (as the estimated start and end don’t match the estimated duration), then adjust the estimated start date to match actual start and estimated duration</text>
+  </threadedComment>
+  <threadedComment ref="L9" dT="2024-11-13T02:22:05.30" personId="{00000000-0000-0000-0000-000000000000}" id="{1E40B37D-EE5E-4ABA-94C6-CD6810B21150}">
+    <text>Student 3’s tasks have no notes. It would be helpful to have them to describe the tasks that student 3 has done and better track the overall state and progress of the project</text>
+  </threadedComment>
+  <threadedComment ref="H11" dT="2024-11-14T04:03:16.07" personId="{00000000-0000-0000-0000-000000000000}" id="{148159F2-9102-4E85-BF1B-E8AE6420CBA1}">
+    <text xml:space="preserve">It seems Student 3 started work on the code before making the use case descriptions and structure diagram. It would be better to do these in reverse order to better structure the code before making it.
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A1" dT="2024-11-14T04:21:50.19" personId="{00000000-0000-0000-0000-000000000000}" id="{0430417D-6521-4777-A475-87A4377C5536}">
+    <text>Task lookup page incomplete</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C7" dT="2024-11-14T04:20:11.21" personId="{00000000-0000-0000-0000-000000000000}" id="{DC7AA41F-FB8B-4CD3-BD51-6F9F13C9B524}">
+    <text>Only two students are named and the categories aren’t listed</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1">
     <tabColor theme="6"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N12"/>
-  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="30" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.69921875" style="3" customWidth="1"/>
-    <col min="2" max="4" width="18.69921875" style="19" customWidth="1"/>
-    <col min="5" max="6" width="18.69921875" style="20" customWidth="1"/>
-    <col min="7" max="8" width="18.69921875" style="19" customWidth="1"/>
-    <col min="9" max="10" width="16.796875" style="20" customWidth="1"/>
+    <col min="1" max="1" width="6.7265625" style="3" customWidth="1"/>
+    <col min="2" max="4" width="18.7265625" style="19" customWidth="1"/>
+    <col min="5" max="6" width="18.7265625" style="20" customWidth="1"/>
+    <col min="7" max="8" width="18.7265625" style="19" customWidth="1"/>
+    <col min="9" max="10" width="16.81640625" style="20" customWidth="1"/>
     <col min="11" max="12" width="16" style="19" customWidth="1"/>
-    <col min="13" max="13" width="20.3984375" style="19" customWidth="1"/>
-    <col min="14" max="14" width="6.69921875" style="3" customWidth="1"/>
-    <col min="15" max="15" width="4.19921875" style="2" customWidth="1"/>
-    <col min="16" max="40" width="3.296875" style="2" customWidth="1"/>
-    <col min="41" max="16384" width="9.09765625" style="2"/>
+    <col min="13" max="13" width="20.36328125" style="19" customWidth="1"/>
+    <col min="14" max="14" width="6.7265625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="4.1796875" style="2" customWidth="1"/>
+    <col min="16" max="40" width="3.26953125" style="2" customWidth="1"/>
+    <col min="41" max="16384" width="9.08984375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="5" customFormat="1" ht="30" customHeight="1">
+    <row r="1" spans="1:14" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -1533,7 +1679,7 @@
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
     </row>
-    <row r="2" spans="1:14" s="5" customFormat="1" ht="80.099999999999994" customHeight="1">
+    <row r="2" spans="1:14" s="5" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="26" t="s">
         <v>0</v>
@@ -1555,7 +1701,7 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
     </row>
-    <row r="3" spans="1:14" s="5" customFormat="1" ht="30" customHeight="1">
+    <row r="3" spans="1:14" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1571,7 +1717,7 @@
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
     </row>
-    <row r="4" spans="1:14" s="5" customFormat="1" ht="62.1" customHeight="1">
+    <row r="4" spans="1:14" s="5" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11"/>
       <c r="B4" s="17" t="s">
         <v>2</v>
@@ -1608,7 +1754,7 @@
       </c>
       <c r="M4" s="11"/>
     </row>
-    <row r="5" spans="1:14" s="5" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="5" spans="1:14" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="18" t="s">
         <v>13</v>
@@ -1647,7 +1793,7 @@
       </c>
       <c r="M5" s="3"/>
     </row>
-    <row r="6" spans="1:14" s="5" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="6" spans="1:14" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="18" t="s">
         <v>16</v>
@@ -1686,7 +1832,7 @@
       </c>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" spans="1:14" s="5" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="7" spans="1:14" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="18" t="s">
         <v>18</v>
@@ -1696,11 +1842,11 @@
       </c>
       <c r="D7" s="25">
         <f ca="1">TODAY()-4</f>
-        <v>45597</v>
+        <v>45605</v>
       </c>
       <c r="E7" s="25">
         <f ca="1">TODAY()-4</f>
-        <v>45597</v>
+        <v>45605</v>
       </c>
       <c r="F7" s="18">
         <v>1</v>
@@ -1711,11 +1857,11 @@
       </c>
       <c r="H7" s="25">
         <f ca="1">TODAY()-4</f>
-        <v>45597</v>
+        <v>45605</v>
       </c>
       <c r="I7" s="25">
         <f ca="1">TODAY()-4</f>
-        <v>45597</v>
+        <v>45605</v>
       </c>
       <c r="J7" s="18">
         <v>1</v>
@@ -1728,7 +1874,7 @@
       </c>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" spans="1:14" s="5" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="8" spans="1:14" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="18" t="s">
         <v>21</v>
@@ -1738,11 +1884,11 @@
       </c>
       <c r="D8" s="25">
         <f ca="1">TODAY()-3</f>
-        <v>45598</v>
+        <v>45606</v>
       </c>
       <c r="E8" s="25">
         <f ca="1">TODAY()-3</f>
-        <v>45598</v>
+        <v>45606</v>
       </c>
       <c r="F8" s="18">
         <v>3</v>
@@ -1753,11 +1899,11 @@
       </c>
       <c r="H8" s="25">
         <f ca="1">TODAY()-3</f>
-        <v>45598</v>
+        <v>45606</v>
       </c>
       <c r="I8" s="25">
         <f ca="1">TODAY()-3</f>
-        <v>45598</v>
+        <v>45606</v>
       </c>
       <c r="J8" s="18">
         <v>5</v>
@@ -1770,7 +1916,7 @@
       </c>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" spans="1:14" s="5" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="9" spans="1:14" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="18" t="s">
         <v>23</v>
@@ -1805,7 +1951,7 @@
       <c r="L9" s="18"/>
       <c r="M9" s="3"/>
     </row>
-    <row r="10" spans="1:14" s="5" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="10" spans="1:14" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="18" t="s">
         <v>25</v>
@@ -1840,7 +1986,7 @@
       <c r="L10" s="18"/>
       <c r="M10" s="3"/>
     </row>
-    <row r="11" spans="1:14" s="5" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="11" spans="1:14" s="5" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="18" t="s">
         <v>26</v>
@@ -1876,7 +2022,7 @@
       <c r="L11" s="18"/>
       <c r="M11" s="3"/>
     </row>
-    <row r="12" spans="1:14" s="5" customFormat="1" ht="30" customHeight="1">
+    <row r="12" spans="1:14" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -1894,12 +2040,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="J5:J11">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>(ABS((J5-F5))/F5)&gt;FlagPercent</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K11">
-    <cfRule type="expression" dxfId="17" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>(ABS((K5-G5))/G5)&gt;FlagPercent</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1925,24 +2071,25 @@
   <pageSetup fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter differentFirst="1"/>
   <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C52F64F2-A0CB-432E-B537-8AB164D6506B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C52F64F2-A0CB-432E-B537-8AB164D6506B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="27" customWidth="1"/>
-    <col min="2" max="2" width="20.09765625" style="27" customWidth="1"/>
-    <col min="3" max="3" width="16.69921875" style="27" customWidth="1"/>
-    <col min="4" max="16384" width="8.69921875" style="27"/>
+    <col min="1" max="1" width="12.7265625" style="27" customWidth="1"/>
+    <col min="2" max="2" width="20.08984375" style="27" customWidth="1"/>
+    <col min="3" max="3" width="16.7265625" style="27" customWidth="1"/>
+    <col min="4" max="16384" width="8.7265625" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
         <v>27</v>
       </c>
@@ -1953,17 +2100,17 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="27" t="s">
         <v>32</v>
       </c>
@@ -1971,31 +2118,32 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2">
     <tabColor theme="7" tint="0.59999389629810485"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.69921875" style="12" customWidth="1"/>
-    <col min="2" max="3" width="18.5" style="23" customWidth="1"/>
-    <col min="4" max="4" width="6.69921875" style="13" customWidth="1"/>
+    <col min="1" max="1" width="6.7265625" style="12" customWidth="1"/>
+    <col min="2" max="3" width="18.453125" style="23" customWidth="1"/>
+    <col min="4" max="4" width="6.7265625" style="13" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" customFormat="1" ht="30" customHeight="1">
+    <row r="1" spans="1:4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12"/>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
     </row>
-    <row r="2" spans="1:4" customFormat="1" ht="80.099999999999994" customHeight="1">
+    <row r="2" spans="1:4" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="16" t="s">
         <v>33</v>
@@ -2003,13 +2151,13 @@
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
     </row>
-    <row r="3" spans="1:4" customFormat="1" ht="30" customHeight="1">
+    <row r="3" spans="1:4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
     </row>
-    <row r="4" spans="1:4" customFormat="1" ht="62.1" customHeight="1">
+    <row r="4" spans="1:4" customFormat="1" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14"/>
       <c r="B4" s="22" t="s">
         <v>34</v>
@@ -2019,7 +2167,7 @@
       </c>
       <c r="D4" s="15"/>
     </row>
-    <row r="5" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="5" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12"/>
       <c r="B5" s="22" t="s">
         <v>36</v>
@@ -2029,7 +2177,7 @@
       </c>
       <c r="D5" s="13"/>
     </row>
-    <row r="6" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="6" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12"/>
       <c r="B6" s="22" t="s">
         <v>38</v>
@@ -2039,7 +2187,7 @@
       </c>
       <c r="D6" s="13"/>
     </row>
-    <row r="7" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="7" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12"/>
       <c r="B7" s="22" t="s">
         <v>40</v>
@@ -2049,7 +2197,7 @@
       </c>
       <c r="D7" s="13"/>
     </row>
-    <row r="8" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="8" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12"/>
       <c r="B8" s="22" t="s">
         <v>41</v>
@@ -2059,7 +2207,7 @@
       </c>
       <c r="D8" s="13"/>
     </row>
-    <row r="9" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="9" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12"/>
       <c r="B9" s="22" t="s">
         <v>43</v>
@@ -2069,7 +2217,7 @@
       </c>
       <c r="D9" s="13"/>
     </row>
-    <row r="10" spans="1:4" customFormat="1" ht="33.950000000000003" customHeight="1">
+    <row r="10" spans="1:4" customFormat="1" ht="33.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="22" t="s">
         <v>45</v>
@@ -2079,7 +2227,7 @@
       </c>
       <c r="D10" s="13"/>
     </row>
-    <row r="11" spans="1:4" customFormat="1" ht="30" customHeight="1">
+    <row r="11" spans="1:4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
@@ -2094,13 +2242,23 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -2120,7 +2278,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="28" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60f5a4f2d2b0abadcf532d48ebf9cb71">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7dd78129e6a1811f84807ad11c651531" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -2432,25 +2590,45 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9066C173-72E5-4455-ACFB-9A7596D30A2B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{648F31BC-5AA3-42BF-80F4-A797E59C4FBD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D99023F8-0F96-4650-8DC3-63EE0BD6CB59}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9066C173-72E5-4455-ACFB-9A7596D30A2B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{648F31BC-5AA3-42BF-80F4-A797E59C4FBD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D99023F8-0F96-4650-8DC3-63EE0BD6CB59}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
